--- a/data/derived_data/3_CommunityComposition/Dataset_1/ps_ITS_rare_expe_D1_20_otu_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_1/ps_ITS_rare_expe_D1_20_otu_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -926,9 +926,6 @@
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_729</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
@@ -1964,7 +1961,7 @@
         <v>2125</v>
       </c>
       <c r="BO2" t="n">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="BP2" t="n">
         <v>2075</v>
@@ -2859,7 +2856,7 @@
         <v>84</v>
       </c>
       <c r="CR4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CS4" t="n">
         <v>56</v>
@@ -9323,7 +9320,7 @@
         <v>114</v>
       </c>
       <c r="CR20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="CS20" t="n">
         <v>0</v>
@@ -9882,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
         <v>17</v>
@@ -11256,7 +11253,7 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BP25" t="n">
         <v>4</v>
@@ -14979,7 +14976,7 @@
         <v>4</v>
       </c>
       <c r="CR34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CS34" t="n">
         <v>0</v>
@@ -16430,7 +16427,7 @@
         <v>17</v>
       </c>
       <c r="AO38" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AP38" t="n">
         <v>0</v>
@@ -18211,7 +18208,7 @@
         <v>123</v>
       </c>
       <c r="CR42" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="CS42" t="n">
         <v>190</v>
@@ -20548,7 +20545,7 @@
         <v>20</v>
       </c>
       <c r="BO48" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BP48" t="n">
         <v>430</v>
@@ -20629,7 +20626,7 @@
         <v>37</v>
       </c>
       <c r="CP48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -20790,10 +20787,10 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N49" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -27422,7 +27419,7 @@
         <v>0</v>
       </c>
       <c r="BQ65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR65" t="n">
         <v>0</v>
@@ -28062,7 +28059,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -28469,7 +28466,7 @@
         <v>26</v>
       </c>
       <c r="N68" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -30166,7 +30163,7 @@
         <v>0</v>
       </c>
       <c r="AO72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -30648,7 +30645,7 @@
         <v>0</v>
       </c>
       <c r="BO73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BP73" t="n">
         <v>0</v>
@@ -31698,7 +31695,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N76" t="n">
         <v>7</v>
@@ -33485,7 +33482,7 @@
         <v>105</v>
       </c>
       <c r="BR80" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BS80" t="n">
         <v>0</v>
@@ -34930,7 +34927,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -35334,7 +35331,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N85" t="n">
         <v>7</v>
@@ -35738,7 +35735,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N86" t="n">
         <v>5</v>
@@ -37761,7 +37758,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -37920,7 +37917,7 @@
         <v>16</v>
       </c>
       <c r="BO91" t="n">
-        <v>3228</v>
+        <v>3230</v>
       </c>
       <c r="BP91" t="n">
         <v>2348</v>
@@ -38973,7 +38970,7 @@
         <v>5</v>
       </c>
       <c r="N94" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -40835,7 +40832,7 @@
         <v>109</v>
       </c>
       <c r="CR98" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="CS98" t="n">
         <v>224</v>
@@ -43800,7 +43797,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -47053,7 +47050,7 @@
         <v>37</v>
       </c>
       <c r="N114" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -50040,7 +50037,7 @@
         <v>0</v>
       </c>
       <c r="BO121" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BP121" t="n">
         <v>10</v>
@@ -51656,7 +51653,7 @@
         <v>0</v>
       </c>
       <c r="BO125" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BP125" t="n">
         <v>0</v>
@@ -55696,7 +55693,7 @@
         <v>0</v>
       </c>
       <c r="BO135" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BP135" t="n">
         <v>17</v>
@@ -56504,7 +56501,7 @@
         <v>0</v>
       </c>
       <c r="BO137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BP137" t="n">
         <v>1</v>
@@ -57399,7 +57396,7 @@
         <v>114</v>
       </c>
       <c r="CR139" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="CS139" t="n">
         <v>217</v>
@@ -62402,10 +62399,10 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N152" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -65401,7 +65398,7 @@
         <v>0</v>
       </c>
       <c r="BR159" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BS159" t="n">
         <v>0</v>
@@ -66287,7 +66284,7 @@
         <v>0</v>
       </c>
       <c r="CR161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CS161" t="n">
         <v>0</v>
@@ -67816,7 +67813,7 @@
         <v>0</v>
       </c>
       <c r="BO165" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BP165" t="n">
         <v>13</v>
@@ -69028,7 +69025,7 @@
         <v>0</v>
       </c>
       <c r="BO168" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BP168" t="n">
         <v>16</v>
@@ -70458,10 +70455,10 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -70491,7 +70488,7 @@
         <v>0</v>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="Q172" t="n">
         <v>0</v>
@@ -70533,10 +70530,10 @@
         <v>0</v>
       </c>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AE172" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF172" t="n">
         <v>0</v>
@@ -70563,10 +70560,10 @@
         <v>0</v>
       </c>
       <c r="AN172" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AO172" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AP172" t="n">
         <v>0</v>
@@ -70593,10 +70590,10 @@
         <v>0</v>
       </c>
       <c r="AX172" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AY172" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AZ172" t="n">
         <v>0</v>
@@ -70623,10 +70620,10 @@
         <v>0</v>
       </c>
       <c r="BH172" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI172" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BJ172" t="n">
         <v>0</v>
@@ -70644,16 +70641,16 @@
         <v>0</v>
       </c>
       <c r="BO172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP172" t="n">
         <v>0</v>
       </c>
       <c r="BQ172" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BR172" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BS172" t="n">
         <v>0</v>
@@ -70662,7 +70659,7 @@
         <v>0</v>
       </c>
       <c r="BU172" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="BV172" t="n">
         <v>0</v>
@@ -70692,10 +70689,10 @@
         <v>0</v>
       </c>
       <c r="CE172" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CF172" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CG172" t="n">
         <v>0</v>
@@ -70710,7 +70707,7 @@
         <v>0</v>
       </c>
       <c r="CK172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL172" t="n">
         <v>0</v>
@@ -70725,22 +70722,22 @@
         <v>0</v>
       </c>
       <c r="CP172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ172" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CR172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CS172" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="CT172" t="n">
         <v>0</v>
       </c>
       <c r="CU172" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="CV172" t="n">
         <v>0</v>
@@ -70770,13 +70767,13 @@
         <v>0</v>
       </c>
       <c r="DE172" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="DF172" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="DG172" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DH172" t="n">
         <v>0</v>
@@ -70824,7 +70821,7 @@
         <v>0</v>
       </c>
       <c r="DW172" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DX172" t="n">
         <v>0</v>
@@ -70845,7 +70842,7 @@
         <v>0</v>
       </c>
       <c r="ED172" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173">
@@ -70862,10 +70859,10 @@
         <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -70895,7 +70892,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
         <v>0</v>
@@ -70937,10 +70934,10 @@
         <v>0</v>
       </c>
       <c r="AD173" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
         <v>0</v>
@@ -70961,16 +70958,16 @@
         <v>0</v>
       </c>
       <c r="AL173" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AM173" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN173" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AO173" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="AP173" t="n">
         <v>0</v>
@@ -70997,10 +70994,10 @@
         <v>0</v>
       </c>
       <c r="AX173" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AY173" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AZ173" t="n">
         <v>0</v>
@@ -71027,10 +71024,10 @@
         <v>0</v>
       </c>
       <c r="BH173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI173" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BJ173" t="n">
         <v>0</v>
@@ -71054,10 +71051,10 @@
         <v>0</v>
       </c>
       <c r="BQ173" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BR173" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BS173" t="n">
         <v>0</v>
@@ -71066,7 +71063,7 @@
         <v>0</v>
       </c>
       <c r="BU173" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="BV173" t="n">
         <v>0</v>
@@ -71096,10 +71093,10 @@
         <v>0</v>
       </c>
       <c r="CE173" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CF173" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CG173" t="n">
         <v>0</v>
@@ -71114,7 +71111,7 @@
         <v>0</v>
       </c>
       <c r="CK173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL173" t="n">
         <v>0</v>
@@ -71132,19 +71129,19 @@
         <v>0</v>
       </c>
       <c r="CQ173" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CR173" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CS173" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="CT173" t="n">
         <v>0</v>
       </c>
       <c r="CU173" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="CV173" t="n">
         <v>0</v>
@@ -71174,13 +71171,13 @@
         <v>0</v>
       </c>
       <c r="DE173" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="DF173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="DG173" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DH173" t="n">
         <v>0</v>
@@ -71228,7 +71225,7 @@
         <v>0</v>
       </c>
       <c r="DW173" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DX173" t="n">
         <v>0</v>
@@ -71249,7 +71246,7 @@
         <v>0</v>
       </c>
       <c r="ED173" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -71272,13 +71269,13 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -71365,10 +71362,10 @@
         <v>0</v>
       </c>
       <c r="AL174" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM174" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN174" t="n">
         <v>0</v>
@@ -71676,13 +71673,13 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -71745,10 +71742,10 @@
         <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF175" t="n">
         <v>0</v>
@@ -71862,7 +71859,7 @@
         <v>0</v>
       </c>
       <c r="BQ175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR175" t="n">
         <v>0</v>
@@ -72074,10 +72071,10 @@
         <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -72149,10 +72146,10 @@
         <v>0</v>
       </c>
       <c r="AD176" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
         <v>0</v>
@@ -72242,7 +72239,7 @@
         <v>0</v>
       </c>
       <c r="BI176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ176" t="n">
         <v>0</v>
@@ -72266,7 +72263,7 @@
         <v>0</v>
       </c>
       <c r="BQ176" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR176" t="n">
         <v>0</v>
@@ -72308,7 +72305,7 @@
         <v>0</v>
       </c>
       <c r="CE176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF176" t="n">
         <v>0</v>
@@ -72472,16 +72469,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -72646,7 +72643,7 @@
         <v>0</v>
       </c>
       <c r="BI177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ177" t="n">
         <v>0</v>
@@ -72685,7 +72682,7 @@
         <v>0</v>
       </c>
       <c r="BV177" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW177" t="n">
         <v>0</v>
@@ -72712,7 +72709,7 @@
         <v>0</v>
       </c>
       <c r="CE177" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF177" t="n">
         <v>0</v>
@@ -72724,7 +72721,7 @@
         <v>0</v>
       </c>
       <c r="CI177" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CJ177" t="n">
         <v>0</v>
@@ -72838,7 +72835,7 @@
         <v>0</v>
       </c>
       <c r="DU177" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="DV177" t="n">
         <v>0</v>
@@ -72876,13 +72873,13 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -72897,7 +72894,7 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -73089,7 +73086,7 @@
         <v>0</v>
       </c>
       <c r="BV178" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW178" t="n">
         <v>0</v>
@@ -73128,7 +73125,7 @@
         <v>0</v>
       </c>
       <c r="CI178" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ178" t="n">
         <v>0</v>
@@ -73242,7 +73239,7 @@
         <v>0</v>
       </c>
       <c r="DU178" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="DV178" t="n">
         <v>0</v>
@@ -73286,7 +73283,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -73301,266 +73298,266 @@
         <v>0</v>
       </c>
       <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
+      <c r="V179" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" t="n">
+        <v>0</v>
+      </c>
+      <c r="X179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>111</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>226</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>98</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>44</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>156</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL179" t="n">
+        <v>57</v>
+      </c>
+      <c r="CM179" t="n">
+        <v>14</v>
+      </c>
+      <c r="CN179" t="n">
+        <v>19</v>
+      </c>
+      <c r="CO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR179" t="n">
         <v>6</v>
       </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
-      </c>
-      <c r="N179" t="n">
-        <v>0</v>
-      </c>
-      <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
-      <c r="S179" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" t="n">
-        <v>0</v>
-      </c>
-      <c r="U179" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" t="n">
-        <v>0</v>
-      </c>
-      <c r="W179" t="n">
-        <v>0</v>
-      </c>
-      <c r="X179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR179" t="n">
-        <v>0</v>
-      </c>
       <c r="CS179" t="n">
         <v>0</v>
       </c>
@@ -73580,7 +73577,7 @@
         <v>0</v>
       </c>
       <c r="CY179" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="CZ179" t="n">
         <v>0</v>
@@ -73601,7 +73598,7 @@
         <v>0</v>
       </c>
       <c r="DF179" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DG179" t="n">
         <v>0</v>
@@ -73625,10 +73622,10 @@
         <v>0</v>
       </c>
       <c r="DN179" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DO179" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="DP179" t="n">
         <v>0</v>
@@ -73667,7 +73664,7 @@
         <v>0</v>
       </c>
       <c r="EB179" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="EC179" t="n">
         <v>0</v>
@@ -73711,10 +73708,10 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N180" t="n">
         <v>0</v>
@@ -73756,10 +73753,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -73783,10 +73780,10 @@
         <v>0</v>
       </c>
       <c r="AJ180" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AK180" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL180" t="n">
         <v>0</v>
@@ -73813,10 +73810,10 @@
         <v>0</v>
       </c>
       <c r="AT180" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AV180" t="n">
         <v>0</v>
@@ -73846,7 +73843,7 @@
         <v>0</v>
       </c>
       <c r="BE180" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF180" t="n">
         <v>0</v>
@@ -73870,10 +73867,10 @@
         <v>0</v>
       </c>
       <c r="BM180" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BN180" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="BO180" t="n">
         <v>0</v>
@@ -73912,7 +73909,7 @@
         <v>0</v>
       </c>
       <c r="CA180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CB180" t="n">
         <v>0</v>
@@ -73945,13 +73942,13 @@
         <v>0</v>
       </c>
       <c r="CL180" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="CM180" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CN180" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CO180" t="n">
         <v>0</v>
@@ -73963,7 +73960,7 @@
         <v>0</v>
       </c>
       <c r="CR180" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CS180" t="n">
         <v>0</v>
@@ -73984,7 +73981,7 @@
         <v>0</v>
       </c>
       <c r="CY180" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="CZ180" t="n">
         <v>0</v>
@@ -74005,7 +74002,7 @@
         <v>0</v>
       </c>
       <c r="DF180" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DG180" t="n">
         <v>0</v>
@@ -74029,10 +74026,10 @@
         <v>0</v>
       </c>
       <c r="DN180" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DO180" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="DP180" t="n">
         <v>0</v>
@@ -74071,7 +74068,7 @@
         <v>0</v>
       </c>
       <c r="EB180" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="EC180" t="n">
         <v>0</v>
@@ -74097,124 +74094,124 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L181" t="n">
+        <v>2</v>
+      </c>
+      <c r="M181" t="n">
+        <v>524</v>
+      </c>
+      <c r="N181" t="n">
+        <v>200</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>955</v>
+      </c>
+      <c r="R181" t="n">
+        <v>1459</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2173</v>
+      </c>
+      <c r="V181" t="n">
+        <v>330</v>
+      </c>
+      <c r="W181" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>159</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>88</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>111</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>196</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>362</v>
+      </c>
+      <c r="AN181" t="n">
         <v>3</v>
       </c>
-      <c r="M181" t="n">
-        <v>10</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" t="n">
-        <v>0</v>
-      </c>
-      <c r="W181" t="n">
-        <v>0</v>
-      </c>
-      <c r="X181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>0</v>
-      </c>
       <c r="AO181" t="n">
         <v>0</v>
       </c>
       <c r="AP181" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AR181" t="n">
         <v>0</v>
       </c>
       <c r="AS181" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT181" t="n">
         <v>0</v>
@@ -74223,10 +74220,10 @@
         <v>0</v>
       </c>
       <c r="AV181" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="AW181" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="AX181" t="n">
         <v>0</v>
@@ -74295,7 +74292,7 @@
         <v>0</v>
       </c>
       <c r="BT181" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BU181" t="n">
         <v>0</v>
@@ -74397,7 +74394,7 @@
         <v>0</v>
       </c>
       <c r="DB181" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="DC181" t="n">
         <v>0</v>
@@ -74421,7 +74418,7 @@
         <v>0</v>
       </c>
       <c r="DJ181" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="DK181" t="n">
         <v>0</v>
@@ -74463,13 +74460,13 @@
         <v>0</v>
       </c>
       <c r="DX181" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="DY181" t="n">
         <v>0</v>
       </c>
       <c r="DZ181" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="EA181" t="n">
         <v>0</v>
@@ -74478,10 +74475,10 @@
         <v>0</v>
       </c>
       <c r="EC181" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="ED181" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="182">
@@ -74501,194 +74498,194 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>1029</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>1018</v>
+        <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>228</v>
+      </c>
+      <c r="N182" t="n">
+        <v>194</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" t="n">
+        <v>0</v>
+      </c>
+      <c r="X182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>182</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>284</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>176</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP182" t="n">
         <v>2</v>
       </c>
-      <c r="M182" t="n">
-        <v>524</v>
-      </c>
-      <c r="N182" t="n">
-        <v>200</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>955</v>
-      </c>
-      <c r="R182" t="n">
-        <v>1459</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>2173</v>
-      </c>
-      <c r="V182" t="n">
-        <v>330</v>
-      </c>
-      <c r="W182" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y182" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z182" t="n">
-        <v>159</v>
-      </c>
-      <c r="AA182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC182" t="n">
-        <v>88</v>
-      </c>
-      <c r="AD182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF182" t="n">
-        <v>56</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>111</v>
-      </c>
-      <c r="AH182" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI182" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL182" t="n">
-        <v>196</v>
-      </c>
-      <c r="AM182" t="n">
-        <v>362</v>
-      </c>
-      <c r="AN182" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP182" t="n">
-        <v>168</v>
-      </c>
-      <c r="AQ182" t="n">
-        <v>165</v>
-      </c>
-      <c r="AR182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS182" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV182" t="n">
-        <v>201</v>
-      </c>
-      <c r="AW182" t="n">
-        <v>161</v>
-      </c>
-      <c r="AX182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP182" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ182" t="n">
         <v>0</v>
       </c>
@@ -74699,7 +74696,7 @@
         <v>0</v>
       </c>
       <c r="BT182" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BU182" t="n">
         <v>0</v>
@@ -74801,7 +74798,7 @@
         <v>0</v>
       </c>
       <c r="DB182" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="DC182" t="n">
         <v>0</v>
@@ -74825,7 +74822,7 @@
         <v>0</v>
       </c>
       <c r="DJ182" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="DK182" t="n">
         <v>0</v>
@@ -74867,13 +74864,13 @@
         <v>0</v>
       </c>
       <c r="DX182" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="DY182" t="n">
         <v>0</v>
       </c>
       <c r="DZ182" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="EA182" t="n">
         <v>0</v>
@@ -74882,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="EC182" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="ED182" t="n">
-        <v>1059</v>
+        <v>140</v>
       </c>
     </row>
     <row r="183">
@@ -74926,10 +74923,10 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>228</v>
+        <v>2</v>
       </c>
       <c r="N183" t="n">
-        <v>194</v>
+        <v>3</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -74950,10 +74947,10 @@
         <v>0</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V183" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W183" t="n">
         <v>0</v>
@@ -74974,7 +74971,7 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -75001,10 +74998,10 @@
         <v>0</v>
       </c>
       <c r="AL183" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AM183" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="AN183" t="n">
         <v>0</v>
@@ -75031,10 +75028,10 @@
         <v>0</v>
       </c>
       <c r="AV183" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="AW183" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="AX183" t="n">
         <v>0</v>
@@ -75064,7 +75061,7 @@
         <v>0</v>
       </c>
       <c r="BG183" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BH183" t="n">
         <v>0</v>
@@ -75091,7 +75088,7 @@
         <v>0</v>
       </c>
       <c r="BP183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ183" t="n">
         <v>0</v>
@@ -75289,7 +75286,7 @@
         <v>0</v>
       </c>
       <c r="ED183" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -75330,265 +75327,265 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" t="n">
+        <v>0</v>
+      </c>
+      <c r="X184" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ184" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR184" t="n">
         <v>1</v>
       </c>
-      <c r="N184" t="n">
+      <c r="BS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>24</v>
+      </c>
+      <c r="BU184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV184" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF184" t="n">
+        <v>11</v>
+      </c>
+      <c r="CG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH184" t="n">
+        <v>63</v>
+      </c>
+      <c r="CI184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR184" t="n">
         <v>3</v>
       </c>
-      <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="n">
-        <v>0</v>
-      </c>
-      <c r="T184" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" t="n">
-        <v>1</v>
-      </c>
-      <c r="V184" t="n">
-        <v>18</v>
-      </c>
-      <c r="W184" t="n">
-        <v>0</v>
-      </c>
-      <c r="X184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR184" t="n">
-        <v>0</v>
-      </c>
       <c r="CS184" t="n">
         <v>0</v>
       </c>
       <c r="CT184" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="CU184" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="CV184" t="n">
         <v>0</v>
@@ -75618,7 +75615,7 @@
         <v>0</v>
       </c>
       <c r="DE184" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="DF184" t="n">
         <v>0</v>
@@ -75627,13 +75624,13 @@
         <v>0</v>
       </c>
       <c r="DH184" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="DI184" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="DJ184" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="DK184" t="n">
         <v>0</v>
@@ -75767,7 +75764,7 @@
         <v>0</v>
       </c>
       <c r="X185" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y185" t="n">
         <v>0</v>
@@ -75785,10 +75782,10 @@
         <v>0</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AF185" t="n">
         <v>0</v>
@@ -75815,10 +75812,10 @@
         <v>0</v>
       </c>
       <c r="AN185" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AO185" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AP185" t="n">
         <v>0</v>
@@ -75845,10 +75842,10 @@
         <v>0</v>
       </c>
       <c r="AX185" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AY185" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AZ185" t="n">
         <v>0</v>
@@ -75902,22 +75899,22 @@
         <v>0</v>
       </c>
       <c r="BQ185" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BR185" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="BS185" t="n">
         <v>0</v>
       </c>
       <c r="BT185" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BU185" t="n">
         <v>0</v>
       </c>
       <c r="BV185" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BW185" t="n">
         <v>0</v>
@@ -75944,16 +75941,16 @@
         <v>0</v>
       </c>
       <c r="CE185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF185" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CG185" t="n">
         <v>0</v>
       </c>
       <c r="CH185" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="CI185" t="n">
         <v>0</v>
@@ -75980,19 +75977,19 @@
         <v>0</v>
       </c>
       <c r="CQ185" t="n">
-        <v>2</v>
+        <v>196</v>
       </c>
       <c r="CR185" t="n">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="CS185" t="n">
         <v>0</v>
       </c>
       <c r="CT185" t="n">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="CU185" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="CV185" t="n">
         <v>0</v>
@@ -76022,7 +76019,7 @@
         <v>0</v>
       </c>
       <c r="DE185" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="DF185" t="n">
         <v>0</v>
@@ -76031,13 +76028,13 @@
         <v>0</v>
       </c>
       <c r="DH185" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="DI185" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="DJ185" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="DK185" t="n">
         <v>0</v>
@@ -76126,10 +76123,10 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -76189,10 +76186,10 @@
         <v>0</v>
       </c>
       <c r="AD186" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AF186" t="n">
         <v>0</v>
@@ -76249,10 +76246,10 @@
         <v>0</v>
       </c>
       <c r="AX186" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AY186" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AZ186" t="n">
         <v>0</v>
@@ -76306,10 +76303,10 @@
         <v>0</v>
       </c>
       <c r="BQ186" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR186" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="BS186" t="n">
         <v>0</v>
@@ -76384,10 +76381,10 @@
         <v>0</v>
       </c>
       <c r="CQ186" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="CR186" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="CS186" t="n">
         <v>0</v>
@@ -76530,10 +76527,10 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -76542,10 +76539,10 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -76946,16 +76943,16 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="Q188" t="n">
         <v>0</v>
@@ -76997,10 +76994,10 @@
         <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF188" t="n">
         <v>0</v>
@@ -77027,10 +77024,10 @@
         <v>0</v>
       </c>
       <c r="AN188" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AO188" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP188" t="n">
         <v>0</v>
@@ -77057,7 +77054,7 @@
         <v>0</v>
       </c>
       <c r="AX188" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AY188" t="n">
         <v>0</v>
@@ -77087,10 +77084,10 @@
         <v>0</v>
       </c>
       <c r="BH188" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI188" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BJ188" t="n">
         <v>0</v>
@@ -77114,10 +77111,10 @@
         <v>0</v>
       </c>
       <c r="BQ188" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BR188" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BS188" t="n">
         <v>0</v>
@@ -77156,13 +77153,13 @@
         <v>0</v>
       </c>
       <c r="CE188" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="CF188" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CG188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CH188" t="n">
         <v>0</v>
@@ -77192,10 +77189,10 @@
         <v>0</v>
       </c>
       <c r="CQ188" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CR188" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CS188" t="n">
         <v>0</v>
@@ -77237,7 +77234,7 @@
         <v>0</v>
       </c>
       <c r="DF188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG188" t="n">
         <v>0</v>
@@ -77288,7 +77285,7 @@
         <v>0</v>
       </c>
       <c r="DW188" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="DX188" t="n">
         <v>0</v>
@@ -77356,10 +77353,10 @@
         <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
         <v>0</v>
@@ -77401,10 +77398,10 @@
         <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
         <v>0</v>
@@ -77431,10 +77428,10 @@
         <v>0</v>
       </c>
       <c r="AN189" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="AO189" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AP189" t="n">
         <v>0</v>
@@ -77461,7 +77458,7 @@
         <v>0</v>
       </c>
       <c r="AX189" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AY189" t="n">
         <v>0</v>
@@ -77491,10 +77488,10 @@
         <v>0</v>
       </c>
       <c r="BH189" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI189" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BJ189" t="n">
         <v>0</v>
@@ -77518,10 +77515,10 @@
         <v>0</v>
       </c>
       <c r="BQ189" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BR189" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS189" t="n">
         <v>0</v>
@@ -77560,13 +77557,13 @@
         <v>0</v>
       </c>
       <c r="CE189" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="CF189" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CG189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CH189" t="n">
         <v>0</v>
@@ -77596,10 +77593,10 @@
         <v>0</v>
       </c>
       <c r="CQ189" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CR189" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CS189" t="n">
         <v>0</v>
@@ -77641,7 +77638,7 @@
         <v>0</v>
       </c>
       <c r="DF189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG189" t="n">
         <v>0</v>
@@ -77692,7 +77689,7 @@
         <v>0</v>
       </c>
       <c r="DW189" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="DX189" t="n">
         <v>0</v>
@@ -77742,10 +77739,10 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -77835,44 +77832,44 @@
         <v>0</v>
       </c>
       <c r="AN190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ190" t="n">
         <v>2</v>
       </c>
-      <c r="AO190" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ190" t="n">
-        <v>0</v>
-      </c>
       <c r="BA190" t="n">
         <v>0</v>
       </c>
@@ -77931,13 +77928,13 @@
         <v>0</v>
       </c>
       <c r="BT190" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="BU190" t="n">
         <v>0</v>
       </c>
       <c r="BV190" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="BW190" t="n">
         <v>0</v>
@@ -77967,7 +77964,7 @@
         <v>0</v>
       </c>
       <c r="CF190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG190" t="n">
         <v>0</v>
@@ -77976,7 +77973,7 @@
         <v>0</v>
       </c>
       <c r="CI190" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CJ190" t="n">
         <v>0</v>
@@ -78054,7 +78051,7 @@
         <v>0</v>
       </c>
       <c r="DI190" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="DJ190" t="n">
         <v>0</v>
@@ -78140,16 +78137,16 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I191" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -78248,7 +78245,7 @@
         <v>0</v>
       </c>
       <c r="AQ191" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AR191" t="n">
         <v>0</v>
@@ -78275,7 +78272,7 @@
         <v>0</v>
       </c>
       <c r="AZ191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA191" t="n">
         <v>0</v>
@@ -78335,13 +78332,13 @@
         <v>0</v>
       </c>
       <c r="BT191" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="BU191" t="n">
         <v>0</v>
       </c>
       <c r="BV191" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="BW191" t="n">
         <v>0</v>
@@ -78380,7 +78377,7 @@
         <v>0</v>
       </c>
       <c r="CI191" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CJ191" t="n">
         <v>0</v>
@@ -78458,7 +78455,7 @@
         <v>0</v>
       </c>
       <c r="DI191" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="DJ191" t="n">
         <v>0</v>
@@ -78538,23 +78535,23 @@
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>5</v>
+      </c>
+      <c r="J192" t="n">
         <v>7</v>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
       <c r="K192" t="n">
         <v>0</v>
       </c>
@@ -78574,7 +78571,7 @@
         <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="R192" t="n">
         <v>0</v>
@@ -78619,7 +78616,7 @@
         <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -78643,16 +78640,16 @@
         <v>0</v>
       </c>
       <c r="AN192" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO192" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AP192" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR192" t="n">
         <v>0</v>
@@ -78676,7 +78673,7 @@
         <v>0</v>
       </c>
       <c r="AY192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ192" t="n">
         <v>0</v>
@@ -78706,7 +78703,7 @@
         <v>0</v>
       </c>
       <c r="BI192" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BJ192" t="n">
         <v>0</v>
@@ -78733,13 +78730,13 @@
         <v>0</v>
       </c>
       <c r="BR192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS192" t="n">
         <v>0</v>
       </c>
       <c r="BT192" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BU192" t="n">
         <v>0</v>
@@ -78772,19 +78769,19 @@
         <v>0</v>
       </c>
       <c r="CE192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CF192" t="n">
         <v>0</v>
       </c>
       <c r="CG192" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CH192" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="CI192" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CJ192" t="n">
         <v>0</v>
@@ -78808,10 +78805,10 @@
         <v>0</v>
       </c>
       <c r="CQ192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CR192" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CS192" t="n">
         <v>0</v>
@@ -78820,7 +78817,7 @@
         <v>0</v>
       </c>
       <c r="CU192" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="CV192" t="n">
         <v>0</v>
@@ -78862,10 +78859,10 @@
         <v>0</v>
       </c>
       <c r="DI192" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="DJ192" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="DK192" t="n">
         <v>0</v>
@@ -78942,22 +78939,22 @@
         <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I193" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -78978,7 +78975,7 @@
         <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>0</v>
@@ -79023,7 +79020,7 @@
         <v>0</v>
       </c>
       <c r="AF193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -79047,16 +79044,16 @@
         <v>0</v>
       </c>
       <c r="AN193" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO193" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AP193" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ193" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AR193" t="n">
         <v>0</v>
@@ -79080,7 +79077,7 @@
         <v>0</v>
       </c>
       <c r="AY193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ193" t="n">
         <v>0</v>
@@ -79110,7 +79107,7 @@
         <v>0</v>
       </c>
       <c r="BI193" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BJ193" t="n">
         <v>0</v>
@@ -79137,13 +79134,13 @@
         <v>0</v>
       </c>
       <c r="BR193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS193" t="n">
         <v>0</v>
       </c>
       <c r="BT193" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BU193" t="n">
         <v>0</v>
@@ -79176,19 +79173,19 @@
         <v>0</v>
       </c>
       <c r="CE193" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CF193" t="n">
         <v>0</v>
       </c>
       <c r="CG193" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CH193" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="CI193" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="CJ193" t="n">
         <v>0</v>
@@ -79212,10 +79209,10 @@
         <v>0</v>
       </c>
       <c r="CQ193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CR193" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CS193" t="n">
         <v>0</v>
@@ -79224,7 +79221,7 @@
         <v>0</v>
       </c>
       <c r="CU193" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="CV193" t="n">
         <v>0</v>
@@ -79266,10 +79263,10 @@
         <v>0</v>
       </c>
       <c r="DI193" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="DJ193" t="n">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="DK193" t="n">
         <v>0</v>
@@ -79352,10 +79349,10 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -79451,10 +79448,10 @@
         <v>0</v>
       </c>
       <c r="AN194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO194" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP194" t="n">
         <v>0</v>
@@ -79750,10 +79747,10 @@
         <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -79780,13 +79777,13 @@
         <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -79804,10 +79801,10 @@
         <v>0</v>
       </c>
       <c r="W195" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X195" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="Y195" t="n">
         <v>0</v>
@@ -79825,10 +79822,10 @@
         <v>0</v>
       </c>
       <c r="AD195" t="n">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="AF195" t="n">
         <v>0</v>
@@ -79855,10 +79852,10 @@
         <v>0</v>
       </c>
       <c r="AN195" t="n">
-        <v>1</v>
+        <v>554</v>
       </c>
       <c r="AO195" t="n">
-        <v>6</v>
+        <v>683</v>
       </c>
       <c r="AP195" t="n">
         <v>0</v>
@@ -79885,10 +79882,10 @@
         <v>0</v>
       </c>
       <c r="AX195" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="AY195" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="AZ195" t="n">
         <v>0</v>
@@ -79915,10 +79912,10 @@
         <v>0</v>
       </c>
       <c r="BH195" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="BI195" t="n">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="BJ195" t="n">
         <v>0</v>
@@ -79942,22 +79939,22 @@
         <v>0</v>
       </c>
       <c r="BQ195" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="BR195" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BS195" t="n">
         <v>0</v>
       </c>
       <c r="BT195" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BU195" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="BV195" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW195" t="n">
         <v>0</v>
@@ -79984,19 +79981,19 @@
         <v>0</v>
       </c>
       <c r="CE195" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="CF195" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="CG195" t="n">
-        <v>0</v>
+        <v>2386</v>
       </c>
       <c r="CH195" t="n">
         <v>0</v>
       </c>
       <c r="CI195" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="CJ195" t="n">
         <v>0</v>
@@ -80020,22 +80017,22 @@
         <v>0</v>
       </c>
       <c r="CQ195" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="CR195" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="CS195" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="CT195" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="CU195" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="CV195" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="CW195" t="n">
         <v>0</v>
@@ -80062,22 +80059,22 @@
         <v>0</v>
       </c>
       <c r="DE195" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="DF195" t="n">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="DG195" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="DH195" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="DI195" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="DJ195" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="DK195" t="n">
         <v>0</v>
@@ -80116,10 +80113,10 @@
         <v>0</v>
       </c>
       <c r="DW195" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="DX195" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="DY195" t="n">
         <v>0</v>
@@ -80128,7 +80125,7 @@
         <v>0</v>
       </c>
       <c r="EA195" t="n">
-        <v>0</v>
+        <v>2277</v>
       </c>
       <c r="EB195" t="n">
         <v>0</v>
@@ -80145,19 +80142,19 @@
         <v>328</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="E196" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -80184,13 +80181,13 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="P196" t="n">
-        <v>1609</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -80208,10 +80205,10 @@
         <v>0</v>
       </c>
       <c r="W196" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X196" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="Y196" t="n">
         <v>0</v>
@@ -80229,10 +80226,10 @@
         <v>0</v>
       </c>
       <c r="AD196" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
         <v>0</v>
@@ -80259,10 +80256,10 @@
         <v>0</v>
       </c>
       <c r="AN196" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="AO196" t="n">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="AP196" t="n">
         <v>0</v>
@@ -80289,10 +80286,10 @@
         <v>0</v>
       </c>
       <c r="AX196" t="n">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="AY196" t="n">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="AZ196" t="n">
         <v>0</v>
@@ -80319,10 +80316,10 @@
         <v>0</v>
       </c>
       <c r="BH196" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="BI196" t="n">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="BJ196" t="n">
         <v>0</v>
@@ -80346,22 +80343,22 @@
         <v>0</v>
       </c>
       <c r="BQ196" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="BR196" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BS196" t="n">
         <v>0</v>
       </c>
       <c r="BT196" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BU196" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="BV196" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BW196" t="n">
         <v>0</v>
@@ -80388,19 +80385,19 @@
         <v>0</v>
       </c>
       <c r="CE196" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="CF196" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="CG196" t="n">
-        <v>2386</v>
+        <v>0</v>
       </c>
       <c r="CH196" t="n">
         <v>0</v>
       </c>
       <c r="CI196" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="CJ196" t="n">
         <v>0</v>
@@ -80424,22 +80421,22 @@
         <v>0</v>
       </c>
       <c r="CQ196" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="CR196" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="CS196" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="CT196" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="CU196" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="CV196" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="CW196" t="n">
         <v>0</v>
@@ -80466,22 +80463,22 @@
         <v>0</v>
       </c>
       <c r="DE196" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="DF196" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="DG196" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="DH196" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="DI196" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="DJ196" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="DK196" t="n">
         <v>0</v>
@@ -80517,13 +80514,13 @@
         <v>0</v>
       </c>
       <c r="DV196" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="DW196" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="DX196" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="DY196" t="n">
         <v>0</v>
@@ -80532,7 +80529,7 @@
         <v>0</v>
       </c>
       <c r="EA196" t="n">
-        <v>2277</v>
+        <v>0</v>
       </c>
       <c r="EB196" t="n">
         <v>0</v>
@@ -80549,13 +80546,13 @@
         <v>329</v>
       </c>
       <c r="B197" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -80564,16 +80561,16 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -80921,7 +80918,7 @@
         <v>0</v>
       </c>
       <c r="DV197" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="DW197" t="n">
         <v>0</v>
@@ -80968,77 +80965,77 @@
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
       </c>
       <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" t="n">
+        <v>0</v>
+      </c>
+      <c r="X198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD198" t="n">
         <v>1</v>
       </c>
-      <c r="K198" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0</v>
-      </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="n">
-        <v>0</v>
-      </c>
-      <c r="V198" t="n">
-        <v>0</v>
-      </c>
-      <c r="W198" t="n">
-        <v>0</v>
-      </c>
-      <c r="X198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>0</v>
-      </c>
       <c r="AE198" t="n">
         <v>0</v>
       </c>
@@ -81067,10 +81064,10 @@
         <v>0</v>
       </c>
       <c r="AN198" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO198" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP198" t="n">
         <v>0</v>
@@ -81127,10 +81124,10 @@
         <v>0</v>
       </c>
       <c r="BH198" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="BI198" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="BJ198" t="n">
         <v>0</v>
@@ -81154,7 +81151,7 @@
         <v>0</v>
       </c>
       <c r="BQ198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR198" t="n">
         <v>0</v>
@@ -81196,10 +81193,10 @@
         <v>0</v>
       </c>
       <c r="CE198" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CF198" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="CG198" t="n">
         <v>0</v>
@@ -81256,7 +81253,7 @@
         <v>0</v>
       </c>
       <c r="CY198" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="CZ198" t="n">
         <v>0</v>
@@ -81274,13 +81271,13 @@
         <v>0</v>
       </c>
       <c r="DE198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF198" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="DG198" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="DH198" t="n">
         <v>0</v>
@@ -81369,7 +81366,7 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -81399,7 +81396,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q199" t="n">
         <v>0</v>
@@ -81441,100 +81438,100 @@
         <v>0</v>
       </c>
       <c r="AD199" t="n">
+        <v>64</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>39</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH199" t="n">
         <v>1</v>
       </c>
-      <c r="AE199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH199" t="n">
-        <v>382</v>
-      </c>
       <c r="BI199" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="BJ199" t="n">
         <v>0</v>
@@ -81558,97 +81555,97 @@
         <v>0</v>
       </c>
       <c r="BQ199" t="n">
+        <v>257</v>
+      </c>
+      <c r="BR199" t="n">
+        <v>49</v>
+      </c>
+      <c r="BS199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU199" t="n">
+        <v>44</v>
+      </c>
+      <c r="BV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ199" t="n">
+        <v>71</v>
+      </c>
+      <c r="CR199" t="n">
         <v>3</v>
       </c>
-      <c r="BR199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE199" t="n">
-        <v>24</v>
-      </c>
-      <c r="CF199" t="n">
-        <v>407</v>
-      </c>
-      <c r="CG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR199" t="n">
-        <v>0</v>
-      </c>
       <c r="CS199" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="CT199" t="n">
         <v>0</v>
       </c>
       <c r="CU199" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="CV199" t="n">
         <v>0</v>
@@ -81660,7 +81657,7 @@
         <v>0</v>
       </c>
       <c r="CY199" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="CZ199" t="n">
         <v>0</v>
@@ -81678,13 +81675,13 @@
         <v>0</v>
       </c>
       <c r="DE199" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF199" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="DG199" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="DH199" t="n">
         <v>0</v>
@@ -81693,7 +81690,7 @@
         <v>0</v>
       </c>
       <c r="DJ199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK199" t="n">
         <v>0</v>
@@ -81773,13 +81770,13 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -81803,7 +81800,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
         <v>0</v>
@@ -81845,10 +81842,10 @@
         <v>0</v>
       </c>
       <c r="AD200" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AE200" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF200" t="n">
         <v>0</v>
@@ -81905,10 +81902,10 @@
         <v>0</v>
       </c>
       <c r="AX200" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AY200" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AZ200" t="n">
         <v>0</v>
@@ -81935,10 +81932,10 @@
         <v>0</v>
       </c>
       <c r="BH200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ200" t="n">
         <v>0</v>
@@ -81962,10 +81959,10 @@
         <v>0</v>
       </c>
       <c r="BQ200" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="BR200" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BS200" t="n">
         <v>0</v>
@@ -81974,7 +81971,7 @@
         <v>0</v>
       </c>
       <c r="BU200" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BV200" t="n">
         <v>0</v>
@@ -82004,7 +82001,7 @@
         <v>0</v>
       </c>
       <c r="CE200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF200" t="n">
         <v>0</v>
@@ -82040,19 +82037,19 @@
         <v>0</v>
       </c>
       <c r="CQ200" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="CR200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CS200" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="CT200" t="n">
         <v>0</v>
       </c>
       <c r="CU200" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="CV200" t="n">
         <v>0</v>
@@ -82097,7 +82094,7 @@
         <v>0</v>
       </c>
       <c r="DJ200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK200" t="n">
         <v>0</v>
@@ -82183,107 +82180,107 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
+        <v>0</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO201" t="n">
         <v>2</v>
       </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="n">
-        <v>0</v>
-      </c>
-      <c r="V201" t="n">
-        <v>0</v>
-      </c>
-      <c r="W201" t="n">
-        <v>0</v>
-      </c>
-      <c r="X201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO201" t="n">
-        <v>0</v>
-      </c>
       <c r="AP201" t="n">
         <v>0</v>
       </c>
@@ -82309,10 +82306,10 @@
         <v>0</v>
       </c>
       <c r="AX201" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY201" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AZ201" t="n">
         <v>0</v>
@@ -82342,7 +82339,7 @@
         <v>0</v>
       </c>
       <c r="BI201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ201" t="n">
         <v>0</v>
@@ -82366,10 +82363,10 @@
         <v>0</v>
       </c>
       <c r="BQ201" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="BR201" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS201" t="n">
         <v>0</v>
@@ -82414,7 +82411,7 @@
         <v>0</v>
       </c>
       <c r="CG201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CH201" t="n">
         <v>0</v>
@@ -82444,19 +82441,19 @@
         <v>0</v>
       </c>
       <c r="CQ201" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="CR201" t="n">
         <v>0</v>
       </c>
       <c r="CS201" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CT201" t="n">
         <v>0</v>
       </c>
       <c r="CU201" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CV201" t="n">
         <v>0</v>
@@ -82495,13 +82492,13 @@
         <v>0</v>
       </c>
       <c r="DH201" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="DI201" t="n">
         <v>0</v>
       </c>
       <c r="DJ201" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DK201" t="n">
         <v>0</v>
@@ -82602,10 +82599,10 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -82653,10 +82650,10 @@
         <v>0</v>
       </c>
       <c r="AD202" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF202" t="n">
         <v>0</v>
@@ -82683,10 +82680,10 @@
         <v>0</v>
       </c>
       <c r="AN202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP202" t="n">
         <v>0</v>
@@ -82713,10 +82710,10 @@
         <v>0</v>
       </c>
       <c r="AX202" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AY202" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ202" t="n">
         <v>0</v>
@@ -82746,7 +82743,7 @@
         <v>0</v>
       </c>
       <c r="BI202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ202" t="n">
         <v>0</v>
@@ -82770,10 +82767,10 @@
         <v>0</v>
       </c>
       <c r="BQ202" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="BR202" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS202" t="n">
         <v>0</v>
@@ -82818,7 +82815,7 @@
         <v>0</v>
       </c>
       <c r="CG202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CH202" t="n">
         <v>0</v>
@@ -82848,19 +82845,19 @@
         <v>0</v>
       </c>
       <c r="CQ202" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="CR202" t="n">
         <v>0</v>
       </c>
       <c r="CS202" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CT202" t="n">
         <v>0</v>
       </c>
       <c r="CU202" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CV202" t="n">
         <v>0</v>
@@ -82899,13 +82896,13 @@
         <v>0</v>
       </c>
       <c r="DH202" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="DI202" t="n">
         <v>0</v>
       </c>
       <c r="DJ202" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DK202" t="n">
         <v>0</v>
@@ -82982,19 +82979,19 @@
         <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -83003,94 +83000,94 @@
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M203" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N203" t="n">
+        <v>27</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="n">
+        <v>18</v>
+      </c>
+      <c r="V203" t="n">
+        <v>7</v>
+      </c>
+      <c r="W203" t="n">
+        <v>68</v>
+      </c>
+      <c r="X203" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM203" t="n">
         <v>5</v>
       </c>
-      <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="n">
-        <v>0</v>
-      </c>
-      <c r="V203" t="n">
-        <v>0</v>
-      </c>
-      <c r="W203" t="n">
-        <v>0</v>
-      </c>
-      <c r="X203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL203" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM203" t="n">
-        <v>0</v>
-      </c>
       <c r="AN203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO203" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP203" t="n">
         <v>0</v>
@@ -83111,7 +83108,7 @@
         <v>0</v>
       </c>
       <c r="AV203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW203" t="n">
         <v>0</v>
@@ -83150,7 +83147,7 @@
         <v>0</v>
       </c>
       <c r="BI203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ203" t="n">
         <v>0</v>
@@ -83348,7 +83345,7 @@
         <v>0</v>
       </c>
       <c r="DW203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DX203" t="n">
         <v>0</v>
@@ -83357,7 +83354,7 @@
         <v>0</v>
       </c>
       <c r="DZ203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA203" t="n">
         <v>0</v>
@@ -83386,19 +83383,19 @@
         <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -83407,19 +83404,19 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N204" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q204" t="n">
         <v>0</v>
@@ -83434,16 +83431,16 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V204" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="X204" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y204" t="n">
         <v>0</v>
@@ -83488,13 +83485,13 @@
         <v>0</v>
       </c>
       <c r="AM204" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO204" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP204" t="n">
         <v>0</v>
@@ -83515,7 +83512,7 @@
         <v>0</v>
       </c>
       <c r="AV204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW204" t="n">
         <v>0</v>
@@ -83554,7 +83551,7 @@
         <v>0</v>
       </c>
       <c r="BI204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ204" t="n">
         <v>0</v>
@@ -83752,7 +83749,7 @@
         <v>0</v>
       </c>
       <c r="DW204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DX204" t="n">
         <v>0</v>
@@ -83761,7 +83758,7 @@
         <v>0</v>
       </c>
       <c r="DZ204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA204" t="n">
         <v>0</v>
@@ -83814,10 +83811,10 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -83919,10 +83916,10 @@
         <v>0</v>
       </c>
       <c r="AV205" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="AW205" t="n">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="AX205" t="n">
         <v>0</v>
@@ -83976,10 +83973,10 @@
         <v>0</v>
       </c>
       <c r="BO205" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="BP205" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="BQ205" t="n">
         <v>0</v>
@@ -84323,10 +84320,10 @@
         <v>0</v>
       </c>
       <c r="AV206" t="n">
-        <v>619</v>
+        <v>5</v>
       </c>
       <c r="AW206" t="n">
-        <v>722</v>
+        <v>3</v>
       </c>
       <c r="AX206" t="n">
         <v>0</v>
@@ -84380,10 +84377,10 @@
         <v>0</v>
       </c>
       <c r="BO206" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BP206" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="BQ206" t="n">
         <v>0</v>
@@ -84581,410 +84578,6 @@
         <v>0</v>
       </c>
       <c r="ED206" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>339</v>
-      </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
-      <c r="C207" t="n">
-        <v>0</v>
-      </c>
-      <c r="D207" t="n">
-        <v>0</v>
-      </c>
-      <c r="E207" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" t="n">
-        <v>0</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" t="n">
-        <v>0</v>
-      </c>
-      <c r="W207" t="n">
-        <v>0</v>
-      </c>
-      <c r="X207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV207" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW207" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY207" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY207" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ207" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA207" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB207" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC207" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED207" t="n">
         <v>0</v>
       </c>
     </row>
